--- a/docs/data/jp/xlsx/285A.xlsx
+++ b/docs/data/jp/xlsx/285A.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC112"/>
+  <dimension ref="A1:AC154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -771,7 +774,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>3월 결산 · IFRS · 2026.4Q = 2026년 3월 결산기 4분기</t>
+          <t>3월 결산 · IFRS · 2027.1Q = 2027년 3월 결산기 1분기</t>
         </is>
       </c>
       <c r="Y2" s="4" t="inlineStr">
@@ -793,62 +796,62 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>2024.1Q</t>
+          <t>2024.2Q</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2024.2Q</t>
+          <t>2024.3Q</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2024.3Q</t>
+          <t>2024.4Q</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.1Q</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -940,16 +943,36 @@
       </c>
       <c r="C4" s="11" t="n"/>
       <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
+      <c r="E4" s="12" t="n">
+        <v>322078</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>428497</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>480911</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>449958</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>347094</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>342799</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <v>448346</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <v>543631</v>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>1002852</v>
+      </c>
+      <c r="N4" s="12" t="n">
+        <v>1767117</v>
+      </c>
       <c r="O4" s="11" t="n"/>
       <c r="P4" s="12" t="n"/>
       <c r="Q4" s="12" t="n"/>
@@ -1423,16 +1446,36 @@
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="21" t="n"/>
       <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="22" t="n"/>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="22" t="n"/>
-      <c r="M11" s="22" t="n"/>
-      <c r="N11" s="22" t="n"/>
+      <c r="E11" s="22" t="n">
+        <v>247291</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>271905</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>284460</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>297584</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>283078</v>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>271620</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>326208</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <v>366991</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <v>359905</v>
+      </c>
+      <c r="N11" s="22" t="n">
+        <v>387051</v>
+      </c>
       <c r="O11" s="21" t="n"/>
       <c r="P11" s="22" t="n"/>
       <c r="Q11" s="22" t="n"/>
@@ -1716,16 +1759,36 @@
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="21" t="n"/>
       <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="22" t="n"/>
-      <c r="K15" s="22" t="n"/>
-      <c r="L15" s="22" t="n"/>
-      <c r="M15" s="22" t="n"/>
-      <c r="N15" s="22" t="n"/>
+      <c r="E15" s="22" t="n">
+        <v>31478</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>31001</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>31631</v>
+      </c>
+      <c r="H15" s="22" t="n">
+        <v>34778</v>
+      </c>
+      <c r="I15" s="22" t="n">
+        <v>30441</v>
+      </c>
+      <c r="J15" s="22" t="n">
+        <v>29847</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>36235</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <v>33847</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <v>46652</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>71727</v>
+      </c>
       <c r="O15" s="21" t="n"/>
       <c r="P15" s="22" t="n"/>
       <c r="Q15" s="22" t="n"/>
@@ -1761,16 +1824,36 @@
       </c>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
+      <c r="E16" s="12" t="n">
+        <v>43858</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>125859</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>166032</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>122715</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>37142</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>44899</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>85921</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>142754</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>596795</v>
+      </c>
+      <c r="N16" s="12" t="n">
+        <v>1270017</v>
+      </c>
       <c r="O16" s="11" t="n"/>
       <c r="P16" s="12" t="n"/>
       <c r="Q16" s="12" t="n"/>
@@ -2712,16 +2795,36 @@
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="21" t="n"/>
       <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="22" t="n"/>
-      <c r="I32" s="22" t="n"/>
-      <c r="J32" s="22" t="n"/>
-      <c r="K32" s="22" t="n"/>
-      <c r="L32" s="22" t="n"/>
-      <c r="M32" s="22" t="n"/>
-      <c r="N32" s="22" t="n"/>
+      <c r="E32" s="22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>1477</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>2586</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>6109</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>4503</v>
+      </c>
+      <c r="J32" s="22" t="n">
+        <v>3921</v>
+      </c>
+      <c r="K32" s="22" t="n">
+        <v>1569</v>
+      </c>
+      <c r="L32" s="22" t="n">
+        <v>1262</v>
+      </c>
+      <c r="M32" s="22" t="n">
+        <v>2150</v>
+      </c>
+      <c r="N32" s="22" t="n">
+        <v>530</v>
+      </c>
       <c r="O32" s="21" t="n"/>
       <c r="P32" s="22" t="n"/>
       <c r="Q32" s="22" t="n"/>
@@ -2888,16 +2991,36 @@
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="21" t="n"/>
       <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="22" t="n"/>
-      <c r="J34" s="22" t="n"/>
-      <c r="K34" s="22" t="n"/>
-      <c r="L34" s="22" t="n"/>
-      <c r="M34" s="22" t="n"/>
-      <c r="N34" s="22" t="n"/>
+      <c r="E34" s="22" t="n">
+        <v>8451</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>1374</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>990</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>936</v>
+      </c>
+      <c r="J34" s="22" t="n">
+        <v>354</v>
+      </c>
+      <c r="K34" s="22" t="n">
+        <v>1551</v>
+      </c>
+      <c r="L34" s="22" t="n">
+        <v>1301</v>
+      </c>
+      <c r="M34" s="22" t="n">
+        <v>1650</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>38852</v>
+      </c>
       <c r="O34" s="21" t="n"/>
       <c r="P34" s="22" t="n"/>
       <c r="Q34" s="22" t="n"/>
@@ -3060,16 +3183,36 @@
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="21" t="n"/>
       <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="22" t="n"/>
-      <c r="I36" s="22" t="n"/>
-      <c r="J36" s="22" t="n"/>
-      <c r="K36" s="22" t="n"/>
-      <c r="L36" s="22" t="n"/>
-      <c r="M36" s="22" t="n"/>
-      <c r="N36" s="22" t="n"/>
+      <c r="E36" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="F36" s="22" t="n">
+        <v>199</v>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>1231</v>
+      </c>
+      <c r="H36" s="22" t="n">
+        <v>1135</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>1142</v>
+      </c>
+      <c r="J36" s="22" t="n">
+        <v>2398</v>
+      </c>
+      <c r="K36" s="22" t="n">
+        <v>-402</v>
+      </c>
+      <c r="L36" s="22" t="n">
+        <v>1608</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <v>5895</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>17170</v>
+      </c>
       <c r="O36" s="21" t="n"/>
       <c r="P36" s="22" t="n"/>
       <c r="Q36" s="22" t="n"/>
@@ -3232,16 +3375,36 @@
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="21" t="n"/>
       <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="J38" s="22" t="n"/>
-      <c r="K38" s="22" t="n"/>
-      <c r="L38" s="22" t="n"/>
-      <c r="M38" s="22" t="n"/>
-      <c r="N38" s="22" t="n"/>
+      <c r="E38" s="22" t="n">
+        <v>26856</v>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>26192</v>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>18282</v>
+      </c>
+      <c r="H38" s="22" t="n">
+        <v>17428</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>23426</v>
+      </c>
+      <c r="J38" s="22" t="n">
+        <v>19860</v>
+      </c>
+      <c r="K38" s="22" t="n">
+        <v>29102</v>
+      </c>
+      <c r="L38" s="22" t="n">
+        <v>22769</v>
+      </c>
+      <c r="M38" s="22" t="n">
+        <v>24977</v>
+      </c>
+      <c r="N38" s="22" t="n">
+        <v>52801</v>
+      </c>
       <c r="O38" s="21" t="n"/>
       <c r="P38" s="22" t="n"/>
       <c r="Q38" s="22" t="n"/>
@@ -3404,16 +3567,36 @@
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="12" t="n"/>
+      <c r="E40" s="12" t="n">
+        <v>17159</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>99746</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>149173</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>106687</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>15063</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>27294</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>56716</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>121740</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>578345</v>
+      </c>
+      <c r="N40" s="12" t="n">
+        <v>1234720</v>
+      </c>
       <c r="O40" s="11" t="n"/>
       <c r="P40" s="12" t="n"/>
       <c r="Q40" s="12" t="n"/>
@@ -3460,16 +3643,36 @@
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="21" t="n"/>
       <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="F41" s="22" t="n"/>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="22" t="n"/>
-      <c r="I41" s="22" t="n"/>
-      <c r="J41" s="22" t="n"/>
-      <c r="K41" s="22" t="n"/>
-      <c r="L41" s="22" t="n"/>
-      <c r="M41" s="22" t="n"/>
-      <c r="N41" s="22" t="n"/>
+      <c r="E41" s="22" t="n">
+        <v>6906</v>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>29988</v>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>42951</v>
+      </c>
+      <c r="H41" s="22" t="n">
+        <v>30612</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>-5203</v>
+      </c>
+      <c r="J41" s="22" t="n">
+        <v>9021</v>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>16046</v>
+      </c>
+      <c r="L41" s="22" t="n">
+        <v>33926</v>
+      </c>
+      <c r="M41" s="22" t="n">
+        <v>170606</v>
+      </c>
+      <c r="N41" s="22" t="n">
+        <v>392549</v>
+      </c>
       <c r="O41" s="21" t="n"/>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="22" t="n"/>
@@ -3631,16 +3834,36 @@
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="n"/>
       <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="12" t="n"/>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="12" t="n"/>
+      <c r="E43" s="12" t="n">
+        <v>10253</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>69758</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>106222</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>76075</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>20266</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>18273</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>40670</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>87814</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>407739</v>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>842171</v>
+      </c>
       <c r="O43" s="11" t="n"/>
       <c r="P43" s="12" t="n"/>
       <c r="Q43" s="12" t="n"/>
@@ -3687,16 +3910,36 @@
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="11" t="n"/>
       <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="12" t="n"/>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="12" t="n"/>
+      <c r="E44" s="12" t="n">
+        <v>10246</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>69758</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>106222</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>76068</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>20267</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>18284</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>40662</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>87810</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>407734</v>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>842165</v>
+      </c>
       <c r="O44" s="11" t="n"/>
       <c r="P44" s="12" t="n"/>
       <c r="Q44" s="12" t="n"/>
@@ -3887,10 +4130,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>12550</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -3925,7 +4170,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>548015088</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5124,7 +5371,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5134,12 +5381,12 @@
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>현금흐름표 · 전 항목</t>
+          <t>손익계산서 · 전 항목</t>
         </is>
       </c>
       <c r="B76" s="44" t="inlineStr">
         <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+          <t>분기 = 3개월 단독</t>
         </is>
       </c>
       <c r="C76" s="18" t="n"/>
@@ -5183,62 +5430,62 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>2024.1Q</t>
+          <t>2024.2Q</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>2024.2Q</t>
+          <t>2024.3Q</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>2024.3Q</t>
+          <t>2024.4Q</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.1Q</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
@@ -5320,845 +5567,3645 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>법인세차감전 이익</t>
-        </is>
+          <t>매출수익</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>322078</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>-343330</v>
+        <v>428497</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>480911</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>449958</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>347094</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>370669</v>
+        <v>342799</v>
+      </c>
+      <c r="K78" s="12" t="n">
+        <v>448346</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <v>543631</v>
+      </c>
+      <c r="M78" s="12" t="n">
+        <v>1002852</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>784095</v>
+        <v>1767117</v>
       </c>
       <c r="V78" s="12" t="n">
-        <v>-343330</v>
+        <v>322078</v>
       </c>
       <c r="W78" s="12" t="n">
-        <v>370669</v>
+        <v>347094</v>
       </c>
       <c r="X78" s="12" t="n">
-        <v>784095</v>
+        <v>1002852</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비 및 상각비</t>
-        </is>
-      </c>
-      <c r="F79" s="22" t="n">
-        <v>346066</v>
-      </c>
-      <c r="J79" s="22" t="n">
-        <v>312307</v>
-      </c>
-      <c r="N79" s="22" t="n">
-        <v>312826</v>
-      </c>
-      <c r="V79" s="22" t="n">
-        <v>346066</v>
-      </c>
-      <c r="W79" s="22" t="n">
-        <v>312307</v>
-      </c>
-      <c r="X79" s="22" t="n">
-        <v>312826</v>
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>매출원가</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="n">
+        <v>247291</v>
       </c>
       <c r="F80" s="22" t="n">
-        <v>764</v>
+        <v>271905</v>
+      </c>
+      <c r="G80" s="22" t="n">
+        <v>284460</v>
+      </c>
+      <c r="H80" s="22" t="n">
+        <v>297584</v>
+      </c>
+      <c r="I80" s="22" t="n">
+        <v>283078</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>30</v>
+        <v>271620</v>
+      </c>
+      <c r="K80" s="22" t="n">
+        <v>326208</v>
+      </c>
+      <c r="L80" s="22" t="n">
+        <v>366991</v>
+      </c>
+      <c r="M80" s="22" t="n">
+        <v>359905</v>
       </c>
       <c r="N80" s="22" t="n">
-        <v>366</v>
+        <v>387051</v>
       </c>
       <c r="V80" s="22" t="n">
-        <v>764</v>
+        <v>247291</v>
       </c>
       <c r="W80" s="22" t="n">
-        <v>30</v>
+        <v>283078</v>
       </c>
       <c r="X80" s="22" t="n">
-        <v>366</v>
+        <v>359905</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>금융수익</t>
-        </is>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>-1847</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>-3707</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>-9499</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>-1847</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>-3707</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>-9499</v>
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>매출총이익</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="n">
+        <v>74787</v>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>156592</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>196451</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>152374</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>64016</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>71179</v>
+      </c>
+      <c r="K81" s="12" t="n">
+        <v>122138</v>
+      </c>
+      <c r="L81" s="12" t="n">
+        <v>176640</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>642947</v>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>1380066</v>
+      </c>
+      <c r="V81" s="12" t="n">
+        <v>74787</v>
+      </c>
+      <c r="W81" s="12" t="n">
+        <v>64016</v>
+      </c>
+      <c r="X81" s="12" t="n">
+        <v>642947</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>금융비용</t>
-        </is>
-      </c>
-      <c r="F82" s="22" t="n">
-        <v>92740</v>
-      </c>
-      <c r="J82" s="22" t="n">
-        <v>85328</v>
-      </c>
-      <c r="N82" s="22" t="n">
-        <v>96708</v>
-      </c>
-      <c r="V82" s="22" t="n">
-        <v>92740</v>
-      </c>
-      <c r="W82" s="22" t="n">
-        <v>85328</v>
-      </c>
-      <c r="X82" s="22" t="n">
-        <v>96708</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>지분법손익</t>
-        </is>
+          <t>판매비와 관리비</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>31478</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>-261</v>
+        <v>31001</v>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>31631</v>
+      </c>
+      <c r="H83" s="22" t="n">
+        <v>34778</v>
+      </c>
+      <c r="I83" s="22" t="n">
+        <v>30441</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>-542</v>
+        <v>29847</v>
+      </c>
+      <c r="K83" s="22" t="n">
+        <v>36235</v>
+      </c>
+      <c r="L83" s="22" t="n">
+        <v>33847</v>
+      </c>
+      <c r="M83" s="22" t="n">
+        <v>46652</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>-935</v>
+        <v>71727</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>-261</v>
+        <v>31478</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>-542</v>
+        <v>30441</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>-935</v>
+        <v>46652</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손익</t>
-        </is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>9000</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-5691</v>
+        <v>1477</v>
+      </c>
+      <c r="G84" s="22" t="n">
+        <v>2586</v>
+      </c>
+      <c r="H84" s="22" t="n">
+        <v>6109</v>
+      </c>
+      <c r="I84" s="22" t="n">
+        <v>4503</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>-6883</v>
+        <v>3921</v>
+      </c>
+      <c r="K84" s="22" t="n">
+        <v>1569</v>
+      </c>
+      <c r="L84" s="22" t="n">
+        <v>1262</v>
+      </c>
+      <c r="M84" s="22" t="n">
+        <v>2150</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>-1168</v>
+        <v>530</v>
       </c>
       <c r="V84" s="22" t="n">
-        <v>-5691</v>
+        <v>9000</v>
       </c>
       <c r="W84" s="22" t="n">
-        <v>-6883</v>
+        <v>4503</v>
       </c>
       <c r="X84" s="22" t="n">
-        <v>-1168</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
+          <t>기타비용</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="n">
+        <v>8451</v>
       </c>
       <c r="F85" s="22" t="n">
-        <v>94472</v>
+        <v>1209</v>
+      </c>
+      <c r="G85" s="22" t="n">
+        <v>1374</v>
+      </c>
+      <c r="H85" s="22" t="n">
+        <v>990</v>
+      </c>
+      <c r="I85" s="22" t="n">
+        <v>936</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>-82092</v>
+        <v>354</v>
+      </c>
+      <c r="K85" s="22" t="n">
+        <v>1551</v>
+      </c>
+      <c r="L85" s="22" t="n">
+        <v>1301</v>
+      </c>
+      <c r="M85" s="22" t="n">
+        <v>1650</v>
       </c>
       <c r="N85" s="22" t="n">
-        <v>-55765</v>
+        <v>38852</v>
       </c>
       <c r="V85" s="22" t="n">
-        <v>94472</v>
+        <v>8451</v>
       </c>
       <c r="W85" s="22" t="n">
-        <v>-82092</v>
+        <v>936</v>
       </c>
       <c r="X85" s="22" t="n">
-        <v>-55765</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>매출채권 및 기타채권 증감액</t>
-        </is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="n">
+        <v>43858</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>-24412</v>
+        <v>125859</v>
+      </c>
+      <c r="G86" s="22" t="n">
+        <v>166032</v>
+      </c>
+      <c r="H86" s="22" t="n">
+        <v>122715</v>
+      </c>
+      <c r="I86" s="22" t="n">
+        <v>37142</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>-89361</v>
+        <v>44899</v>
+      </c>
+      <c r="K86" s="22" t="n">
+        <v>85921</v>
+      </c>
+      <c r="L86" s="22" t="n">
+        <v>142754</v>
+      </c>
+      <c r="M86" s="22" t="n">
+        <v>596795</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>-397696</v>
+        <v>1270017</v>
       </c>
       <c r="V86" s="22" t="n">
-        <v>-24412</v>
+        <v>43858</v>
       </c>
       <c r="W86" s="22" t="n">
-        <v>-89361</v>
+        <v>37142</v>
       </c>
       <c r="X86" s="22" t="n">
-        <v>-397696</v>
+        <v>596795</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>매입채무 및 기타채무 증감액</t>
-        </is>
-      </c>
-      <c r="F87" s="22" t="n">
-        <v>75944</v>
-      </c>
-      <c r="J87" s="22" t="n">
-        <v>-12373</v>
-      </c>
-      <c r="N87" s="22" t="n">
-        <v>53165</v>
-      </c>
-      <c r="V87" s="22" t="n">
-        <v>75944</v>
-      </c>
-      <c r="W87" s="22" t="n">
-        <v>-12373</v>
-      </c>
-      <c r="X87" s="22" t="n">
-        <v>53165</v>
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="E87" s="17">
+        <f>IF(OR(E86="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E86/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F87" s="17">
+        <f>IF(OR(F86="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F86/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G87" s="17">
+        <f>IF(OR(G86="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G86/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H87" s="17">
+        <f>IF(OR(H86="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H86/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I87" s="17">
+        <f>IF(OR(I86="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I86/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J87" s="17">
+        <f>IF(OR(J86="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J86/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K87" s="17">
+        <f>IF(OR(K86="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K86/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L87" s="17">
+        <f>IF(OR(L86="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L86/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M87" s="17">
+        <f>IF(OR(M86="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M86/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N87" s="17">
+        <f>IF(OR(N86="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N86/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="V87" s="17">
+        <f>IF(OR(V86="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V86/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W87" s="17">
+        <f>IF(OR(W86="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W86/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X87" s="17">
+        <f>IF(OR(X86="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X86/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="F88" s="22" t="n">
-        <v>-1652</v>
-      </c>
-      <c r="J88" s="22" t="n">
-        <v>376</v>
-      </c>
-      <c r="N88" s="22" t="n">
-        <v>-744</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>-1652</v>
-      </c>
-      <c r="W88" s="22" t="n">
-        <v>376</v>
-      </c>
-      <c r="X88" s="22" t="n">
-        <v>-744</v>
+      <c r="A88" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G88" s="17">
+        <f>IF(OR(G86="",C86=""),"",IF(C86&lt;=0,"",IFERROR(G86/C86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H88" s="17">
+        <f>IF(OR(H86="",D86=""),"",IF(D86&lt;=0,"",IFERROR(H86/D86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I88" s="17">
+        <f>IF(OR(I86="",E86=""),"",IF(E86&lt;=0,"",IFERROR(I86/E86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J88" s="17">
+        <f>IF(OR(J86="",F86=""),"",IF(F86&lt;=0,"",IFERROR(J86/F86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K88" s="17">
+        <f>IF(OR(K86="",G86=""),"",IF(G86&lt;=0,"",IFERROR(K86/G86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L88" s="17">
+        <f>IF(OR(L86="",H86=""),"",IF(H86&lt;=0,"",IFERROR(L86/H86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M88" s="17">
+        <f>IF(OR(M86="",I86=""),"",IF(I86&lt;=0,"",IFERROR(M86/I86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N88" s="17">
+        <f>IF(OR(N86="",J86=""),"",IF(J86&lt;=0,"",IFERROR(N86/J86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V88" s="17">
+        <f>IF(OR(V86="",U86=""),"",IF(U86&lt;=0,"",IFERROR(V86/U86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W88" s="17">
+        <f>IF(OR(W86="",V86=""),"",IF(V86&lt;=0,"",IFERROR(W86/V86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X88" s="17">
+        <f>IF(OR(X86="",W86=""),"",IF(W86&lt;=0,"",IFERROR(X86/W86-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
+          <t>금융수익</t>
+        </is>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>11</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>-4297</v>
+        <v>199</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>1231</v>
+      </c>
+      <c r="H89" s="22" t="n">
+        <v>1135</v>
+      </c>
+      <c r="I89" s="22" t="n">
+        <v>1142</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>-8700</v>
+        <v>2398</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>-402</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>1608</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>5895</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>-20703</v>
+        <v>17170</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>-4297</v>
+        <v>11</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>-8700</v>
+        <v>1142</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>-20703</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
-        </is>
+          <t>금융비용</t>
+        </is>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>26856</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>228496</v>
+        <v>26192</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>18282</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>17428</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>23426</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>565052</v>
+        <v>19860</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>29102</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>22769</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>24977</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>760650</v>
+        <v>52801</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>228496</v>
+        <v>26856</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>565052</v>
+        <v>23426</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>760650</v>
+        <v>24977</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
-        </is>
+          <t>지분법이익</t>
+        </is>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>146</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>2717</v>
+        <v>-120</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>192</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>265</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>205</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>3366</v>
+        <v>-143</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>299</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>147</v>
+      </c>
+      <c r="M91" s="22" t="n">
+        <v>632</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>4019</v>
+        <v>334</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>2717</v>
+        <v>146</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>3366</v>
+        <v>205</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>4019</v>
+        <v>632</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>이자 지급</t>
-        </is>
-      </c>
-      <c r="F92" s="22" t="n">
-        <v>-32333</v>
-      </c>
-      <c r="J92" s="22" t="n">
-        <v>-82409</v>
-      </c>
-      <c r="N92" s="22" t="n">
-        <v>-88709</v>
-      </c>
-      <c r="V92" s="22" t="n">
-        <v>-32333</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>-82409</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>-88709</v>
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>법인세비용차감전 중간이익</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>17159</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>99746</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>149173</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>106687</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>15063</v>
+      </c>
+      <c r="J92" s="12" t="n">
+        <v>27294</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>56716</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>121740</v>
+      </c>
+      <c r="M92" s="12" t="n">
+        <v>578345</v>
+      </c>
+      <c r="N92" s="12" t="n">
+        <v>1234720</v>
+      </c>
+      <c r="V92" s="12" t="n">
+        <v>17159</v>
+      </c>
+      <c r="W92" s="12" t="n">
+        <v>15063</v>
+      </c>
+      <c r="X92" s="12" t="n">
+        <v>578345</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>Income Taxes Refund Paid Ope CF</t>
-        </is>
+          <t>Income Tax Expense</t>
+        </is>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>6906</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>-3769</v>
+        <v>29988</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>42951</v>
+      </c>
+      <c r="H93" s="22" t="n">
+        <v>30612</v>
+      </c>
+      <c r="I93" s="22" t="n">
+        <v>-5203</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>-9593</v>
+        <v>9021</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>16046</v>
+      </c>
+      <c r="L93" s="22" t="n">
+        <v>33926</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>170606</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>-59420</v>
+        <v>392549</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>-3769</v>
+        <v>6906</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>-9593</v>
+        <v>-5203</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>-59420</v>
+        <v>170606</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>영업활동 현금흐름</t>
-        </is>
+          <t>중간이익</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>10253</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>195111</v>
+        <v>69758</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>106222</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>76075</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>20266</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>476416</v>
+        <v>18273</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>40670</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <v>87814</v>
+      </c>
+      <c r="M94" s="12" t="n">
+        <v>407739</v>
       </c>
       <c r="N94" s="12" t="n">
-        <v>616540</v>
+        <v>842171</v>
       </c>
       <c r="V94" s="12" t="n">
-        <v>195111</v>
+        <v>10253</v>
       </c>
       <c r="W94" s="12" t="n">
-        <v>476416</v>
+        <v>20266</v>
       </c>
       <c r="X94" s="12" t="n">
-        <v>616540</v>
+        <v>407739</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
+          <t>기본 주당 중간이익(엔)</t>
+        </is>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>1.979999999999996e-05</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>-304436</v>
+        <v>0.0001348</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>0.00020526</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>0.00014588</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>3.402000000000004e-05</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>-223847</v>
+        <v>3.39e-05</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>7.536000000000001e-05</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>0.00016241</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>0.0007523999999999999</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>-281062</v>
+        <v>0.00153991</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>-304436</v>
+        <v>1.979999999999996e-05</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>-223847</v>
+        <v>3.402000000000004e-05</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>-281062</v>
+        <v>0.0007523999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
+          <t>희석 주당 중간이익(엔)</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>1.979999999999996e-05</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>11346</v>
+        <v>0.00013316</v>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>0.00020279</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>0.00014535</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>3.415000000000004e-05</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>8820</v>
+        <v>3.375e-05</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>7.465000000000001e-05</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>0.00015954</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>0.0007412100000000001</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>6254</v>
+        <v>0.00152509</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>11346</v>
+        <v>1.979999999999996e-05</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>8820</v>
+        <v>3.415000000000004e-05</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>6254</v>
+        <v>0.0007412100000000001</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>무형자산 취득 지출</t>
-        </is>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>-661</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>-1756</v>
-      </c>
-      <c r="N97" s="22" t="n">
-        <v>-2612</v>
-      </c>
-      <c r="V97" s="22" t="n">
-        <v>-661</v>
-      </c>
-      <c r="W97" s="22" t="n">
-        <v>-1756</v>
-      </c>
-      <c r="X97" s="22" t="n">
-        <v>-2612</v>
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Profit Loss Attributable To Owners Of Parent</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>10246</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>69758</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>106222</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>76068</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>20267</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>18284</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>40662</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>87810</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>407734</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>842165</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>10246</v>
+      </c>
+      <c r="W97" s="12" t="n">
+        <v>20267</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>407734</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>Proceeds From Government Grants Inv CF</t>
-        </is>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>18562</v>
-      </c>
-      <c r="J98" s="22" t="n">
-        <v>43748</v>
-      </c>
-      <c r="N98" s="22" t="n">
-        <v>56396</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>18562</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>43748</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>56396</v>
+      <c r="A98" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G98" s="17">
+        <f>IF(OR(G97="",C97=""),"",IF(C97&lt;=0,"",IFERROR(G97/C97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H98" s="17">
+        <f>IF(OR(H97="",D97=""),"",IF(D97&lt;=0,"",IFERROR(H97/D97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I98" s="17">
+        <f>IF(OR(I97="",E97=""),"",IF(E97&lt;=0,"",IFERROR(I97/E97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J98" s="17">
+        <f>IF(OR(J97="",F97=""),"",IF(F97&lt;=0,"",IFERROR(J97/F97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF(OR(K97="",G97=""),"",IF(G97&lt;=0,"",IFERROR(K97/G97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L98" s="17">
+        <f>IF(OR(L97="",H97=""),"",IF(H97&lt;=0,"",IFERROR(L97/H97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M98" s="17">
+        <f>IF(OR(M97="",I97=""),"",IF(I97&lt;=0,"",IFERROR(M97/I97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N98" s="17">
+        <f>IF(OR(N97="",J97=""),"",IF(J97&lt;=0,"",IFERROR(N97/J97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V98" s="17">
+        <f>IF(OR(V97="",U97=""),"",IF(U97&lt;=0,"",IFERROR(V97/U97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W98" s="17">
+        <f>IF(OR(W97="",V97=""),"",IF(V97&lt;=0,"",IFERROR(W97/V97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X98" s="17">
+        <f>IF(OR(X97="",W97=""),"",IF(W97&lt;=0,"",IFERROR(X97/W97-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>336</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="N99" s="22" t="n">
-        <v>-488</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>336</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="X99" s="22" t="n">
-        <v>-488</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>-274853</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>-173011</v>
-      </c>
-      <c r="N100" s="12" t="n">
-        <v>-221512</v>
-      </c>
-      <c r="V100" s="12" t="n">
-        <v>-274853</v>
-      </c>
-      <c r="W100" s="12" t="n">
-        <v>-173011</v>
-      </c>
-      <c r="X100" s="12" t="n">
-        <v>-221512</v>
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>비지배지분</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>Net Increase Decrease In Short Term Borrowings Fin CF</t>
-        </is>
-      </c>
-      <c r="F101" s="22" t="n">
-        <v>91082</v>
-      </c>
-      <c r="J101" s="22" t="n">
-        <v>-126400</v>
-      </c>
-      <c r="V101" s="22" t="n">
-        <v>91082</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>-126400</v>
-      </c>
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B101" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="18" t="n"/>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="n"/>
+      <c r="I101" s="18" t="n"/>
+      <c r="J101" s="18" t="n"/>
+      <c r="K101" s="18" t="n"/>
+      <c r="L101" s="18" t="n"/>
+      <c r="M101" s="18" t="n"/>
+      <c r="N101" s="18" t="n"/>
+      <c r="O101" s="18" t="n"/>
+      <c r="P101" s="18" t="n"/>
+      <c r="Q101" s="18" t="n"/>
+      <c r="R101" s="18" t="n"/>
+      <c r="S101" s="18" t="n"/>
+      <c r="T101" s="18" t="n"/>
+      <c r="U101" s="18" t="n"/>
+      <c r="V101" s="18" t="n"/>
+      <c r="W101" s="18" t="n"/>
+      <c r="X101" s="18" t="n"/>
+      <c r="Y101" s="18" t="n"/>
+      <c r="Z101" s="18" t="n"/>
+      <c r="AA101" s="18" t="n"/>
+      <c r="AB101" s="18" t="n"/>
+      <c r="AC101" s="18" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>Net Increase Decrease In Short Term Borrowings And Revolving Credit Facility Balances Executed Fin CF</t>
-        </is>
-      </c>
-      <c r="J102" s="22" t="n">
-        <v>-126400</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>-126400</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>0</v>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O102" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P102" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q102" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R102" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S102" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T102" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U102" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V102" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W102" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X102" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y102" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z102" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA102" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB102" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC102" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>Proceeds From Long Term Borrowings Fin CF</t>
-        </is>
-      </c>
-      <c r="F103" s="22" t="n">
-        <v>168148</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>68020</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>535637</v>
-      </c>
-      <c r="V103" s="22" t="n">
-        <v>168148</v>
-      </c>
-      <c r="W103" s="22" t="n">
-        <v>68020</v>
-      </c>
-      <c r="X103" s="22" t="n">
-        <v>535637</v>
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>중간이익</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>10253</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>69758</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>106222</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>76075</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>20266</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>18273</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>40670</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>87814</v>
+      </c>
+      <c r="M103" s="12" t="n">
+        <v>407739</v>
+      </c>
+      <c r="N103" s="12" t="n">
+        <v>842171</v>
+      </c>
+      <c r="V103" s="12" t="n">
+        <v>10253</v>
+      </c>
+      <c r="W103" s="12" t="n">
+        <v>20266</v>
+      </c>
+      <c r="X103" s="12" t="n">
+        <v>407739</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
+          <t>Net Change In Fair Value Of Equity Instruments Designated As Measured At Fair Value Through Other Comprehensive Income Net Of Tax Items That Will Not Be Reclassified To Profit Or Loss OCI</t>
+        </is>
+      </c>
+      <c r="E104" s="22" t="n">
+        <v>16198</v>
       </c>
       <c r="F104" s="22" t="n">
-        <v>-228461</v>
+        <v>-4039</v>
+      </c>
+      <c r="G104" s="22" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="H104" s="22" t="n">
+        <v>4817</v>
+      </c>
+      <c r="I104" s="22" t="n">
+        <v>-3918</v>
       </c>
       <c r="J104" s="22" t="n">
-        <v>-265879</v>
+        <v>2868</v>
+      </c>
+      <c r="K104" s="22" t="n">
+        <v>15217</v>
+      </c>
+      <c r="L104" s="22" t="n">
+        <v>54627</v>
+      </c>
+      <c r="M104" s="22" t="n">
+        <v>7597</v>
       </c>
       <c r="N104" s="22" t="n">
-        <v>-616429</v>
+        <v>148622</v>
       </c>
       <c r="V104" s="22" t="n">
-        <v>-228461</v>
+        <v>16198</v>
       </c>
       <c r="W104" s="22" t="n">
-        <v>-265879</v>
+        <v>-3918</v>
       </c>
       <c r="X104" s="22" t="n">
-        <v>-616429</v>
+        <v>7597</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>사채 발행</t>
-        </is>
+          <t>확정급여제도 재측정</t>
+        </is>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>-283</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="22" t="n">
+        <v>1650</v>
       </c>
       <c r="J105" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="L105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="22" t="n">
+        <v>2005</v>
+      </c>
       <c r="N105" s="22" t="n">
-        <v>326656</v>
+        <v>1</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>-283</v>
       </c>
       <c r="W105" s="22" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="X105" s="22" t="n">
-        <v>326656</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환 지출</t>
-        </is>
+          <t>Total Of Items That Will Not Be Reclassified To Profit Or Loss OCI</t>
+        </is>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>15915</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>-27531</v>
+        <v>-4037</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>4817</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>-2268</v>
       </c>
       <c r="J106" s="22" t="n">
-        <v>-28787</v>
+        <v>2871</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>15217</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>54627</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>9602</v>
       </c>
       <c r="N106" s="22" t="n">
-        <v>-30528</v>
+        <v>148623</v>
       </c>
       <c r="V106" s="22" t="n">
-        <v>-27531</v>
+        <v>15915</v>
       </c>
       <c r="W106" s="22" t="n">
-        <v>-28787</v>
+        <v>-2268</v>
       </c>
       <c r="X106" s="22" t="n">
-        <v>-30528</v>
+        <v>9602</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>Redemption Of Preferred Shares Fin CF</t>
-        </is>
+          <t>Exchange Differences On Translation Of Foreign Operations Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+        </is>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>2335</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>3683</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>-6222</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>4821</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>-3808</v>
       </c>
       <c r="J107" s="22" t="n">
-        <v>0</v>
+        <v>1633</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>603</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>2651</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>1291</v>
       </c>
       <c r="N107" s="22" t="n">
-        <v>-322996</v>
+        <v>1929</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>2335</v>
       </c>
       <c r="W107" s="22" t="n">
-        <v>0</v>
+        <v>-3808</v>
       </c>
       <c r="X107" s="22" t="n">
-        <v>-322996</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
+          <t>Effective Portion Of Cash Flow Hedges Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+        </is>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>756</v>
       </c>
       <c r="F108" s="22" t="n">
-        <v>0</v>
+        <v>-5490</v>
+      </c>
+      <c r="G108" s="22" t="n">
+        <v>18120</v>
+      </c>
+      <c r="H108" s="22" t="n">
+        <v>-14812</v>
+      </c>
+      <c r="I108" s="22" t="n">
+        <v>4305</v>
       </c>
       <c r="J108" s="22" t="n">
-        <v>30367</v>
+        <v>-356</v>
+      </c>
+      <c r="K108" s="22" t="n">
+        <v>1389</v>
+      </c>
+      <c r="L108" s="22" t="n">
+        <v>5306</v>
+      </c>
+      <c r="M108" s="22" t="n">
+        <v>-2682</v>
       </c>
       <c r="N108" s="22" t="n">
-        <v>11588</v>
+        <v>3072</v>
       </c>
       <c r="V108" s="22" t="n">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="W108" s="22" t="n">
-        <v>30367</v>
+        <v>4305</v>
       </c>
       <c r="X108" s="22" t="n">
-        <v>11588</v>
+        <v>-2682</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
+          <t>Share Of Other Comprehensive Income Of Investments Accounted For Using Equity Method Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+        </is>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="F109" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G109" s="22" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H109" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="I109" s="22" t="n">
+        <v>-17</v>
       </c>
       <c r="J109" s="22" t="n">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="K109" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L109" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="M109" s="22" t="n">
+        <v>24</v>
       </c>
       <c r="N109" s="22" t="n">
-        <v>-2</v>
+        <v>3</v>
+      </c>
+      <c r="V109" s="22" t="n">
+        <v>22</v>
       </c>
       <c r="W109" s="22" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="X109" s="22" t="n">
-        <v>-2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>3238</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>-322679</v>
-      </c>
-      <c r="N110" s="12" t="n">
-        <v>-96074</v>
-      </c>
-      <c r="V110" s="12" t="n">
-        <v>3238</v>
-      </c>
-      <c r="W110" s="12" t="n">
-        <v>-322679</v>
-      </c>
-      <c r="X110" s="12" t="n">
-        <v>-96074</v>
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>Total Of Items That May Be Reclassified To Profit Or Loss OCI</t>
+        </is>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>3113</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>-1796</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>11877</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>-9974</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>480</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>1271</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>1996</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>7966</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>-1367</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>5004</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>3113</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>480</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>-1367</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>19028</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>-5833</v>
+      </c>
+      <c r="G111" s="22" t="n">
+        <v>-1962</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>-5157</v>
+      </c>
+      <c r="I111" s="22" t="n">
+        <v>-1788</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>4142</v>
+      </c>
+      <c r="K111" s="22" t="n">
+        <v>17213</v>
+      </c>
+      <c r="L111" s="22" t="n">
+        <v>62593</v>
+      </c>
+      <c r="M111" s="22" t="n">
+        <v>8235</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>153627</v>
+      </c>
+      <c r="V111" s="22" t="n">
+        <v>19028</v>
+      </c>
+      <c r="W111" s="22" t="n">
+        <v>-1788</v>
+      </c>
+      <c r="X111" s="22" t="n">
+        <v>8235</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>29281</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>63925</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>104260</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>70918</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>18478</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>22415</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>57883</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>150407</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>415974</v>
+      </c>
+      <c r="N112" s="12" t="n">
+        <v>995798</v>
+      </c>
+      <c r="V112" s="12" t="n">
+        <v>29281</v>
+      </c>
+      <c r="W112" s="12" t="n">
+        <v>18478</v>
+      </c>
+      <c r="X112" s="12" t="n">
+        <v>415974</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>Comprehensive Income Attributable To Owners Of Parent</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>29272</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>63919</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>104272</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>70902</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <v>18488</v>
+      </c>
+      <c r="J113" s="12" t="n">
+        <v>22413</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>57877</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>150401</v>
+      </c>
+      <c r="M113" s="12" t="n">
+        <v>415969</v>
+      </c>
+      <c r="N113" s="12" t="n">
+        <v>995790</v>
+      </c>
+      <c r="V113" s="12" t="n">
+        <v>29272</v>
+      </c>
+      <c r="W113" s="12" t="n">
+        <v>18488</v>
+      </c>
+      <c r="X113" s="12" t="n">
+        <v>415969</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>비지배지분</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M114" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N114" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V114" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W114" s="12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X114" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B116" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+      <c r="J116" s="18" t="n"/>
+      <c r="K116" s="18" t="n"/>
+      <c r="L116" s="18" t="n"/>
+      <c r="M116" s="18" t="n"/>
+      <c r="N116" s="18" t="n"/>
+      <c r="O116" s="18" t="n"/>
+      <c r="P116" s="18" t="n"/>
+      <c r="Q116" s="18" t="n"/>
+      <c r="R116" s="18" t="n"/>
+      <c r="S116" s="18" t="n"/>
+      <c r="T116" s="18" t="n"/>
+      <c r="U116" s="18" t="n"/>
+      <c r="V116" s="18" t="n"/>
+      <c r="W116" s="18" t="n"/>
+      <c r="X116" s="18" t="n"/>
+      <c r="Y116" s="18" t="n"/>
+      <c r="Z116" s="18" t="n"/>
+      <c r="AA116" s="18" t="n"/>
+      <c r="AB116" s="18" t="n"/>
+      <c r="AC116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O117" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S117" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T117" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U117" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V117" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W117" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X117" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y117" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z117" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA117" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB117" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC117" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>법인세비용차감전 중간이익</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="n">
+        <v>-360489</v>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>-343330</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>99746</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>248919</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>355606</v>
+      </c>
+      <c r="I118" s="12" t="n">
+        <v>370669</v>
+      </c>
+      <c r="J118" s="12" t="n">
+        <v>27294</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>84010</v>
+      </c>
+      <c r="L118" s="12" t="n">
+        <v>205750</v>
+      </c>
+      <c r="M118" s="12" t="n">
+        <v>784095</v>
+      </c>
+      <c r="N118" s="12" t="n">
+        <v>1234720</v>
+      </c>
+      <c r="V118" s="12" t="n">
+        <v>-343330</v>
+      </c>
+      <c r="W118" s="12" t="n">
+        <v>370669</v>
+      </c>
+      <c r="X118" s="12" t="n">
+        <v>784095</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>감가상각비 및 상각비</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>264473</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>346066</v>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>78493</v>
+      </c>
+      <c r="G119" s="22" t="n">
+        <v>157685</v>
+      </c>
+      <c r="H119" s="22" t="n">
+        <v>234796</v>
+      </c>
+      <c r="I119" s="22" t="n">
+        <v>312307</v>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>79987</v>
+      </c>
+      <c r="K119" s="22" t="n">
+        <v>158839</v>
+      </c>
+      <c r="L119" s="22" t="n">
+        <v>236419</v>
+      </c>
+      <c r="M119" s="22" t="n">
+        <v>312826</v>
+      </c>
+      <c r="N119" s="22" t="n">
+        <v>76082</v>
+      </c>
+      <c r="V119" s="22" t="n">
+        <v>346066</v>
+      </c>
+      <c r="W119" s="22" t="n">
+        <v>312307</v>
+      </c>
+      <c r="X119" s="22" t="n">
+        <v>312826</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="D120" s="22" t="n">
+        <v>437</v>
+      </c>
+      <c r="E120" s="22" t="n">
+        <v>764</v>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H120" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I120" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="K120" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="L120" s="22" t="n">
+        <v>214</v>
+      </c>
+      <c r="M120" s="22" t="n">
+        <v>366</v>
+      </c>
+      <c r="N120" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="V120" s="22" t="n">
+        <v>764</v>
+      </c>
+      <c r="W120" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="X120" s="22" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
+        <is>
+          <t>금융수익</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>-1836</v>
+      </c>
+      <c r="E121" s="22" t="n">
+        <v>-1847</v>
+      </c>
+      <c r="F121" s="22" t="n">
+        <v>-199</v>
+      </c>
+      <c r="G121" s="22" t="n">
+        <v>-1430</v>
+      </c>
+      <c r="H121" s="22" t="n">
+        <v>-2565</v>
+      </c>
+      <c r="I121" s="22" t="n">
+        <v>-3707</v>
+      </c>
+      <c r="J121" s="22" t="n">
+        <v>-2398</v>
+      </c>
+      <c r="K121" s="22" t="n">
+        <v>-1996</v>
+      </c>
+      <c r="L121" s="22" t="n">
+        <v>-3604</v>
+      </c>
+      <c r="M121" s="22" t="n">
+        <v>-9499</v>
+      </c>
+      <c r="N121" s="22" t="n">
+        <v>-17170</v>
+      </c>
+      <c r="V121" s="22" t="n">
+        <v>-1847</v>
+      </c>
+      <c r="W121" s="22" t="n">
+        <v>-3707</v>
+      </c>
+      <c r="X121" s="22" t="n">
+        <v>-9499</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>금융비용</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>65884</v>
+      </c>
+      <c r="E122" s="22" t="n">
+        <v>92740</v>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>26192</v>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>44474</v>
+      </c>
+      <c r="H122" s="22" t="n">
+        <v>61902</v>
+      </c>
+      <c r="I122" s="22" t="n">
+        <v>85328</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>19860</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>48962</v>
+      </c>
+      <c r="L122" s="22" t="n">
+        <v>71731</v>
+      </c>
+      <c r="M122" s="22" t="n">
+        <v>96708</v>
+      </c>
+      <c r="N122" s="22" t="n">
+        <v>52801</v>
+      </c>
+      <c r="V122" s="22" t="n">
+        <v>92740</v>
+      </c>
+      <c r="W122" s="22" t="n">
+        <v>85328</v>
+      </c>
+      <c r="X122" s="22" t="n">
+        <v>96708</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>지분법손익</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E123" s="22" t="n">
+        <v>-261</v>
+      </c>
+      <c r="F123" s="22" t="n">
+        <v>120</v>
+      </c>
+      <c r="G123" s="22" t="n">
+        <v>-72</v>
+      </c>
+      <c r="H123" s="22" t="n">
+        <v>-337</v>
+      </c>
+      <c r="I123" s="22" t="n">
+        <v>-542</v>
+      </c>
+      <c r="J123" s="22" t="n">
+        <v>143</v>
+      </c>
+      <c r="K123" s="22" t="n">
+        <v>-156</v>
+      </c>
+      <c r="L123" s="22" t="n">
+        <v>-303</v>
+      </c>
+      <c r="M123" s="22" t="n">
+        <v>-935</v>
+      </c>
+      <c r="N123" s="22" t="n">
+        <v>-334</v>
+      </c>
+      <c r="V123" s="22" t="n">
+        <v>-261</v>
+      </c>
+      <c r="W123" s="22" t="n">
+        <v>-542</v>
+      </c>
+      <c r="X123" s="22" t="n">
+        <v>-935</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 제각·매각손익</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="n">
+        <v>1643</v>
+      </c>
+      <c r="E124" s="22" t="n">
+        <v>-5691</v>
+      </c>
+      <c r="F124" s="22" t="n">
+        <v>-419</v>
+      </c>
+      <c r="G124" s="22" t="n">
+        <v>-825</v>
+      </c>
+      <c r="H124" s="22" t="n">
+        <v>-3639</v>
+      </c>
+      <c r="I124" s="22" t="n">
+        <v>-6883</v>
+      </c>
+      <c r="J124" s="22" t="n">
+        <v>-2541</v>
+      </c>
+      <c r="K124" s="22" t="n">
+        <v>-2154</v>
+      </c>
+      <c r="L124" s="22" t="n">
+        <v>-1726</v>
+      </c>
+      <c r="M124" s="22" t="n">
+        <v>-1168</v>
+      </c>
+      <c r="N124" s="22" t="n">
+        <v>1096</v>
+      </c>
+      <c r="V124" s="22" t="n">
+        <v>-5691</v>
+      </c>
+      <c r="W124" s="22" t="n">
+        <v>-6883</v>
+      </c>
+      <c r="X124" s="22" t="n">
+        <v>-1168</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="inlineStr">
+        <is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="n">
+        <v>141975</v>
+      </c>
+      <c r="E125" s="22" t="n">
+        <v>94472</v>
+      </c>
+      <c r="F125" s="22" t="n">
+        <v>-31702</v>
+      </c>
+      <c r="G125" s="22" t="n">
+        <v>-61776</v>
+      </c>
+      <c r="H125" s="22" t="n">
+        <v>-72670</v>
+      </c>
+      <c r="I125" s="22" t="n">
+        <v>-82092</v>
+      </c>
+      <c r="J125" s="22" t="n">
+        <v>-18336</v>
+      </c>
+      <c r="K125" s="22" t="n">
+        <v>-7595</v>
+      </c>
+      <c r="L125" s="22" t="n">
+        <v>1996</v>
+      </c>
+      <c r="M125" s="22" t="n">
+        <v>-55765</v>
+      </c>
+      <c r="N125" s="22" t="n">
+        <v>-23004</v>
+      </c>
+      <c r="V125" s="22" t="n">
+        <v>94472</v>
+      </c>
+      <c r="W125" s="22" t="n">
+        <v>-82092</v>
+      </c>
+      <c r="X125" s="22" t="n">
+        <v>-55765</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>매출채권 및 기타채권 증감액</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="n">
+        <v>-17551</v>
+      </c>
+      <c r="E126" s="22" t="n">
+        <v>-24412</v>
+      </c>
+      <c r="F126" s="22" t="n">
+        <v>-48364</v>
+      </c>
+      <c r="G126" s="22" t="n">
+        <v>-80459</v>
+      </c>
+      <c r="H126" s="22" t="n">
+        <v>-187030</v>
+      </c>
+      <c r="I126" s="22" t="n">
+        <v>-89361</v>
+      </c>
+      <c r="J126" s="22" t="n">
+        <v>24831</v>
+      </c>
+      <c r="K126" s="22" t="n">
+        <v>4191</v>
+      </c>
+      <c r="L126" s="22" t="n">
+        <v>-94645</v>
+      </c>
+      <c r="M126" s="22" t="n">
+        <v>-397696</v>
+      </c>
+      <c r="N126" s="22" t="n">
+        <v>-472052</v>
+      </c>
+      <c r="V126" s="22" t="n">
+        <v>-24412</v>
+      </c>
+      <c r="W126" s="22" t="n">
+        <v>-89361</v>
+      </c>
+      <c r="X126" s="22" t="n">
+        <v>-397696</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
+        <is>
+          <t>매입채무 및 기타채무 증감액</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="n">
+        <v>33083</v>
+      </c>
+      <c r="E127" s="22" t="n">
+        <v>75944</v>
+      </c>
+      <c r="F127" s="22" t="n">
+        <v>45954</v>
+      </c>
+      <c r="G127" s="22" t="n">
+        <v>36941</v>
+      </c>
+      <c r="H127" s="22" t="n">
+        <v>66489</v>
+      </c>
+      <c r="I127" s="22" t="n">
+        <v>-12373</v>
+      </c>
+      <c r="J127" s="22" t="n">
+        <v>-8946</v>
+      </c>
+      <c r="K127" s="22" t="n">
+        <v>14878</v>
+      </c>
+      <c r="L127" s="22" t="n">
+        <v>77437</v>
+      </c>
+      <c r="M127" s="22" t="n">
+        <v>53165</v>
+      </c>
+      <c r="N127" s="22" t="n">
+        <v>14329</v>
+      </c>
+      <c r="V127" s="22" t="n">
+        <v>75944</v>
+      </c>
+      <c r="W127" s="22" t="n">
+        <v>-12373</v>
+      </c>
+      <c r="X127" s="22" t="n">
+        <v>53165</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>퇴직급여부채 증감</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>821</v>
+      </c>
+      <c r="E128" s="22" t="n">
+        <v>-1652</v>
+      </c>
+      <c r="F128" s="22" t="n">
+        <v>280</v>
+      </c>
+      <c r="G128" s="22" t="n">
+        <v>435</v>
+      </c>
+      <c r="H128" s="22" t="n">
+        <v>470</v>
+      </c>
+      <c r="I128" s="22" t="n">
+        <v>376</v>
+      </c>
+      <c r="J128" s="22" t="n">
+        <v>-161</v>
+      </c>
+      <c r="K128" s="22" t="n">
+        <v>-342</v>
+      </c>
+      <c r="L128" s="22" t="n">
+        <v>-416</v>
+      </c>
+      <c r="M128" s="22" t="n">
+        <v>-744</v>
+      </c>
+      <c r="N128" s="22" t="n">
+        <v>-29</v>
+      </c>
+      <c r="V128" s="22" t="n">
+        <v>-1652</v>
+      </c>
+      <c r="W128" s="22" t="n">
+        <v>376</v>
+      </c>
+      <c r="X128" s="22" t="n">
+        <v>-744</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="n">
+        <v>-476</v>
+      </c>
+      <c r="E129" s="22" t="n">
+        <v>-4297</v>
+      </c>
+      <c r="F129" s="22" t="n">
+        <v>-23590</v>
+      </c>
+      <c r="G129" s="22" t="n">
+        <v>-34287</v>
+      </c>
+      <c r="H129" s="22" t="n">
+        <v>-600</v>
+      </c>
+      <c r="I129" s="22" t="n">
+        <v>-8700</v>
+      </c>
+      <c r="J129" s="22" t="n">
+        <v>10611</v>
+      </c>
+      <c r="K129" s="22" t="n">
+        <v>-20193</v>
+      </c>
+      <c r="L129" s="22" t="n">
+        <v>-40437</v>
+      </c>
+      <c r="M129" s="22" t="n">
+        <v>-20703</v>
+      </c>
+      <c r="N129" s="22" t="n">
+        <v>105854</v>
+      </c>
+      <c r="V129" s="22" t="n">
+        <v>-4297</v>
+      </c>
+      <c r="W129" s="22" t="n">
+        <v>-8700</v>
+      </c>
+      <c r="X129" s="22" t="n">
+        <v>-20703</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n">
+        <v>127849</v>
+      </c>
+      <c r="E130" s="22" t="n">
+        <v>228496</v>
+      </c>
+      <c r="F130" s="22" t="n">
+        <v>146513</v>
+      </c>
+      <c r="G130" s="22" t="n">
+        <v>309611</v>
+      </c>
+      <c r="H130" s="22" t="n">
+        <v>452433</v>
+      </c>
+      <c r="I130" s="22" t="n">
+        <v>565052</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>130414</v>
+      </c>
+      <c r="K130" s="22" t="n">
+        <v>278570</v>
+      </c>
+      <c r="L130" s="22" t="n">
+        <v>452416</v>
+      </c>
+      <c r="M130" s="22" t="n">
+        <v>760650</v>
+      </c>
+      <c r="N130" s="22" t="n">
+        <v>972322</v>
+      </c>
+      <c r="V130" s="22" t="n">
+        <v>228496</v>
+      </c>
+      <c r="W130" s="22" t="n">
+        <v>565052</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>760650</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>2717</v>
+      </c>
+      <c r="F131" s="22" t="n">
+        <v>294</v>
+      </c>
+      <c r="G131" s="22" t="n">
+        <v>1513</v>
+      </c>
+      <c r="H131" s="22" t="n">
+        <v>2010</v>
+      </c>
+      <c r="I131" s="22" t="n">
+        <v>3366</v>
+      </c>
+      <c r="J131" s="22" t="n">
+        <v>248</v>
+      </c>
+      <c r="K131" s="22" t="n">
+        <v>2246</v>
+      </c>
+      <c r="L131" s="22" t="n">
+        <v>3042</v>
+      </c>
+      <c r="M131" s="22" t="n">
+        <v>4019</v>
+      </c>
+      <c r="N131" s="22" t="n">
+        <v>387</v>
+      </c>
+      <c r="V131" s="22" t="n">
+        <v>2717</v>
+      </c>
+      <c r="W131" s="22" t="n">
+        <v>3366</v>
+      </c>
+      <c r="X131" s="22" t="n">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="n">
+        <v>-23419</v>
+      </c>
+      <c r="E132" s="22" t="n">
+        <v>-32333</v>
+      </c>
+      <c r="F132" s="22" t="n">
+        <v>-46628</v>
+      </c>
+      <c r="G132" s="22" t="n">
+        <v>-63171</v>
+      </c>
+      <c r="H132" s="22" t="n">
+        <v>-73309</v>
+      </c>
+      <c r="I132" s="22" t="n">
+        <v>-82409</v>
+      </c>
+      <c r="J132" s="22" t="n">
+        <v>-32733</v>
+      </c>
+      <c r="K132" s="22" t="n">
+        <v>-67405</v>
+      </c>
+      <c r="L132" s="22" t="n">
+        <v>-75208</v>
+      </c>
+      <c r="M132" s="22" t="n">
+        <v>-88709</v>
+      </c>
+      <c r="N132" s="22" t="n">
+        <v>-5839</v>
+      </c>
+      <c r="V132" s="22" t="n">
+        <v>-32333</v>
+      </c>
+      <c r="W132" s="22" t="n">
+        <v>-82409</v>
+      </c>
+      <c r="X132" s="22" t="n">
+        <v>-88709</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t>Income Taxes Refund Paid Ope CF</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>-4677</v>
+      </c>
+      <c r="E133" s="22" t="n">
+        <v>-3769</v>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>-5037</v>
+      </c>
+      <c r="G133" s="22" t="n">
+        <v>-6088</v>
+      </c>
+      <c r="H133" s="22" t="n">
+        <v>-8574</v>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>-9593</v>
+      </c>
+      <c r="J133" s="22" t="n">
+        <v>-36823</v>
+      </c>
+      <c r="K133" s="22" t="n">
+        <v>-38259</v>
+      </c>
+      <c r="L133" s="22" t="n">
+        <v>-58083</v>
+      </c>
+      <c r="M133" s="22" t="n">
+        <v>-59420</v>
+      </c>
+      <c r="N133" s="22" t="n">
+        <v>-100533</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>-3769</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>-9593</v>
+      </c>
+      <c r="X133" s="22" t="n">
+        <v>-59420</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="n">
+        <v>101885</v>
+      </c>
+      <c r="E134" s="12" t="n">
+        <v>195111</v>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>95142</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>241865</v>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>372560</v>
+      </c>
+      <c r="I134" s="12" t="n">
+        <v>476416</v>
+      </c>
+      <c r="J134" s="12" t="n">
+        <v>61106</v>
+      </c>
+      <c r="K134" s="12" t="n">
+        <v>175152</v>
+      </c>
+      <c r="L134" s="12" t="n">
+        <v>322167</v>
+      </c>
+      <c r="M134" s="12" t="n">
+        <v>616540</v>
+      </c>
+      <c r="N134" s="12" t="n">
+        <v>866337</v>
+      </c>
+      <c r="V134" s="12" t="n">
+        <v>195111</v>
+      </c>
+      <c r="W134" s="12" t="n">
+        <v>476416</v>
+      </c>
+      <c r="X134" s="12" t="n">
+        <v>616540</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>-261095</v>
+      </c>
+      <c r="E135" s="22" t="n">
+        <v>-304436</v>
+      </c>
+      <c r="F135" s="22" t="n">
+        <v>-46091</v>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>-87252</v>
+      </c>
+      <c r="H135" s="22" t="n">
+        <v>-145000</v>
+      </c>
+      <c r="I135" s="22" t="n">
+        <v>-223847</v>
+      </c>
+      <c r="J135" s="22" t="n">
+        <v>-52512</v>
+      </c>
+      <c r="K135" s="22" t="n">
+        <v>-143127</v>
+      </c>
+      <c r="L135" s="22" t="n">
+        <v>-213688</v>
+      </c>
+      <c r="M135" s="22" t="n">
+        <v>-281062</v>
+      </c>
+      <c r="N135" s="22" t="n">
+        <v>-51176</v>
+      </c>
+      <c r="V135" s="22" t="n">
+        <v>-304436</v>
+      </c>
+      <c r="W135" s="22" t="n">
+        <v>-223847</v>
+      </c>
+      <c r="X135" s="22" t="n">
+        <v>-281062</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="n">
+        <v>1554</v>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>11346</v>
+      </c>
+      <c r="F136" s="22" t="n">
+        <v>724</v>
+      </c>
+      <c r="G136" s="22" t="n">
+        <v>1623</v>
+      </c>
+      <c r="H136" s="22" t="n">
+        <v>4072</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>8820</v>
+      </c>
+      <c r="J136" s="22" t="n">
+        <v>3945</v>
+      </c>
+      <c r="K136" s="22" t="n">
+        <v>4820</v>
+      </c>
+      <c r="L136" s="22" t="n">
+        <v>5847</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>6254</v>
+      </c>
+      <c r="N136" s="22" t="n">
+        <v>1217</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>11346</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>8820</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>6254</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>무형자산 취득 지출</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>-529</v>
+      </c>
+      <c r="E137" s="22" t="n">
+        <v>-661</v>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>-75</v>
+      </c>
+      <c r="G137" s="22" t="n">
+        <v>-204</v>
+      </c>
+      <c r="H137" s="22" t="n">
+        <v>-302</v>
+      </c>
+      <c r="I137" s="22" t="n">
+        <v>-1756</v>
+      </c>
+      <c r="J137" s="22" t="n">
+        <v>-1065</v>
+      </c>
+      <c r="K137" s="22" t="n">
+        <v>-1923</v>
+      </c>
+      <c r="L137" s="22" t="n">
+        <v>-2295</v>
+      </c>
+      <c r="M137" s="22" t="n">
+        <v>-2612</v>
+      </c>
+      <c r="N137" s="22" t="n">
+        <v>-1226</v>
+      </c>
+      <c r="V137" s="22" t="n">
+        <v>-661</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-1756</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>-2612</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>Proceeds From Government Grants Inv CFIFRS</t>
+        </is>
+      </c>
+      <c r="F138" s="22" t="n">
+        <v>14398</v>
+      </c>
+      <c r="J138" s="22" t="n">
+        <v>15525</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>Proceeds From Government Grants Inv CF</t>
+        </is>
+      </c>
+      <c r="D139" s="22" t="n">
+        <v>10846</v>
+      </c>
+      <c r="E139" s="22" t="n">
+        <v>18562</v>
+      </c>
+      <c r="G139" s="22" t="n">
+        <v>22966</v>
+      </c>
+      <c r="H139" s="22" t="n">
+        <v>25436</v>
+      </c>
+      <c r="I139" s="22" t="n">
+        <v>43748</v>
+      </c>
+      <c r="J139" s="22" t="n">
+        <v>15525</v>
+      </c>
+      <c r="K139" s="22" t="n">
+        <v>33355</v>
+      </c>
+      <c r="L139" s="22" t="n">
+        <v>41934</v>
+      </c>
+      <c r="M139" s="22" t="n">
+        <v>56396</v>
+      </c>
+      <c r="N139" s="22" t="n">
+        <v>12026</v>
+      </c>
+      <c r="V139" s="22" t="n">
+        <v>18562</v>
+      </c>
+      <c r="W139" s="22" t="n">
+        <v>43748</v>
+      </c>
+      <c r="X139" s="22" t="n">
+        <v>56396</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>Purchase Of Other Financial Assets Inv CF</t>
+        </is>
+      </c>
+      <c r="J140" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="22" t="n">
+        <v>-78220</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="n">
+        <v>119</v>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>336</v>
+      </c>
+      <c r="F141" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G141" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H141" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="I141" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="J141" s="22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K141" s="22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L141" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M141" s="22" t="n">
+        <v>-488</v>
+      </c>
+      <c r="N141" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="V141" s="22" t="n">
+        <v>336</v>
+      </c>
+      <c r="W141" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="X141" s="22" t="n">
+        <v>-488</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="n">
+        <v>-249105</v>
+      </c>
+      <c r="E142" s="12" t="n">
+        <v>-274853</v>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>-31038</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>-62842</v>
+      </c>
+      <c r="H142" s="12" t="n">
+        <v>-115758</v>
+      </c>
+      <c r="I142" s="12" t="n">
+        <v>-173011</v>
+      </c>
+      <c r="J142" s="12" t="n">
+        <v>-34122</v>
+      </c>
+      <c r="K142" s="12" t="n">
+        <v>-106882</v>
+      </c>
+      <c r="L142" s="12" t="n">
+        <v>-168192</v>
+      </c>
+      <c r="M142" s="12" t="n">
+        <v>-221512</v>
+      </c>
+      <c r="N142" s="12" t="n">
+        <v>-117318</v>
+      </c>
+      <c r="V142" s="12" t="n">
+        <v>-274853</v>
+      </c>
+      <c r="W142" s="12" t="n">
+        <v>-173011</v>
+      </c>
+      <c r="X142" s="12" t="n">
+        <v>-221512</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>Net Increase Decrease In Short Term Borrowings And Revolving Credit Facility Balances Executed Fin CF</t>
+        </is>
+      </c>
+      <c r="G143" s="22" t="n">
+        <v>-93806</v>
+      </c>
+      <c r="H143" s="22" t="n">
+        <v>-126400</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>-126400</v>
+      </c>
+      <c r="K143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>-126400</v>
+      </c>
+      <c r="X143" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="n">
+        <v>191065</v>
+      </c>
+      <c r="E144" s="22" t="n">
+        <v>91082</v>
+      </c>
+      <c r="F144" s="22" t="n">
+        <v>-12564</v>
+      </c>
+      <c r="H144" s="22" t="n">
+        <v>-126400</v>
+      </c>
+      <c r="I144" s="22" t="n">
+        <v>-126400</v>
+      </c>
+      <c r="J144" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" s="22" t="n">
+        <v>91082</v>
+      </c>
+      <c r="W144" s="22" t="n">
+        <v>-126400</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>Proceeds From Long Term Borrowings Fin CF</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="n">
+        <v>95438</v>
+      </c>
+      <c r="E145" s="22" t="n">
+        <v>168148</v>
+      </c>
+      <c r="F145" s="22" t="n">
+        <v>12749</v>
+      </c>
+      <c r="G145" s="22" t="n">
+        <v>26448</v>
+      </c>
+      <c r="H145" s="22" t="n">
+        <v>47667</v>
+      </c>
+      <c r="I145" s="22" t="n">
+        <v>68020</v>
+      </c>
+      <c r="J145" s="22" t="n">
+        <v>43487</v>
+      </c>
+      <c r="K145" s="22" t="n">
+        <v>507212</v>
+      </c>
+      <c r="L145" s="22" t="n">
+        <v>516161</v>
+      </c>
+      <c r="M145" s="22" t="n">
+        <v>535637</v>
+      </c>
+      <c r="N145" s="22" t="n">
+        <v>7498</v>
+      </c>
+      <c r="V145" s="22" t="n">
+        <v>168148</v>
+      </c>
+      <c r="W145" s="22" t="n">
+        <v>68020</v>
+      </c>
+      <c r="X145" s="22" t="n">
+        <v>535637</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="inlineStr">
+        <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="n">
+        <v>-171143</v>
+      </c>
+      <c r="E146" s="22" t="n">
+        <v>-228461</v>
+      </c>
+      <c r="F146" s="22" t="n">
+        <v>-77151</v>
+      </c>
+      <c r="G146" s="22" t="n">
+        <v>-140137</v>
+      </c>
+      <c r="H146" s="22" t="n">
+        <v>-202745</v>
+      </c>
+      <c r="I146" s="22" t="n">
+        <v>-265879</v>
+      </c>
+      <c r="J146" s="22" t="n">
+        <v>-63499</v>
+      </c>
+      <c r="K146" s="22" t="n">
+        <v>-498817</v>
+      </c>
+      <c r="L146" s="22" t="n">
+        <v>-549792</v>
+      </c>
+      <c r="M146" s="22" t="n">
+        <v>-616429</v>
+      </c>
+      <c r="N146" s="22" t="n">
+        <v>-433226</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>-228461</v>
+      </c>
+      <c r="W146" s="22" t="n">
+        <v>-265879</v>
+      </c>
+      <c r="X146" s="22" t="n">
+        <v>-616429</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20" t="inlineStr">
+        <is>
+          <t>사채 발행</t>
+        </is>
+      </c>
+      <c r="G147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" s="22" t="n">
+        <v>326656</v>
+      </c>
+      <c r="L147" s="22" t="n">
+        <v>326656</v>
+      </c>
+      <c r="M147" s="22" t="n">
+        <v>326656</v>
+      </c>
+      <c r="W147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" s="22" t="n">
+        <v>326656</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환 지출</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>-20651</v>
+      </c>
+      <c r="E148" s="22" t="n">
+        <v>-27531</v>
+      </c>
+      <c r="F148" s="22" t="n">
+        <v>-7191</v>
+      </c>
+      <c r="G148" s="22" t="n">
+        <v>-14223</v>
+      </c>
+      <c r="H148" s="22" t="n">
+        <v>-20666</v>
+      </c>
+      <c r="I148" s="22" t="n">
+        <v>-28787</v>
+      </c>
+      <c r="J148" s="22" t="n">
+        <v>-7455</v>
+      </c>
+      <c r="K148" s="22" t="n">
+        <v>-14712</v>
+      </c>
+      <c r="L148" s="22" t="n">
+        <v>-22554</v>
+      </c>
+      <c r="M148" s="22" t="n">
+        <v>-30528</v>
+      </c>
+      <c r="N148" s="22" t="n">
+        <v>-7929</v>
+      </c>
+      <c r="V148" s="22" t="n">
+        <v>-27531</v>
+      </c>
+      <c r="W148" s="22" t="n">
+        <v>-28787</v>
+      </c>
+      <c r="X148" s="22" t="n">
+        <v>-30528</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20" t="inlineStr">
+        <is>
+          <t>Redemption Of Preferred Shares Fin CF</t>
+        </is>
+      </c>
+      <c r="G149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="22" t="n">
+        <v>-322996</v>
+      </c>
+      <c r="L149" s="22" t="n">
+        <v>-322996</v>
+      </c>
+      <c r="M149" s="22" t="n">
+        <v>-322996</v>
+      </c>
+      <c r="W149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" s="22" t="n">
+        <v>-322996</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="22" t="n">
+        <v>29879</v>
+      </c>
+      <c r="I150" s="22" t="n">
+        <v>30367</v>
+      </c>
+      <c r="J150" s="22" t="n">
+        <v>190</v>
+      </c>
+      <c r="K150" s="22" t="n">
+        <v>651</v>
+      </c>
+      <c r="L150" s="22" t="n">
+        <v>8891</v>
+      </c>
+      <c r="M150" s="22" t="n">
+        <v>11588</v>
+      </c>
+      <c r="N150" s="22" t="n">
+        <v>3311</v>
+      </c>
+      <c r="V150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" s="22" t="n">
+        <v>30367</v>
+      </c>
+      <c r="X150" s="22" t="n">
+        <v>11588</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="H151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M151" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N151" s="22" t="n">
+        <v>-18</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D152" s="12" t="n">
+        <v>94709</v>
+      </c>
+      <c r="E152" s="12" t="n">
+        <v>3238</v>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>-84157</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>-221718</v>
+      </c>
+      <c r="H152" s="12" t="n">
+        <v>-272265</v>
+      </c>
+      <c r="I152" s="12" t="n">
+        <v>-322679</v>
+      </c>
+      <c r="J152" s="12" t="n">
+        <v>-17277</v>
+      </c>
+      <c r="K152" s="12" t="n">
+        <v>-2006</v>
+      </c>
+      <c r="L152" s="12" t="n">
+        <v>-43634</v>
+      </c>
+      <c r="M152" s="12" t="n">
+        <v>-96074</v>
+      </c>
+      <c r="N152" s="12" t="n">
+        <v>-430364</v>
+      </c>
+      <c r="V152" s="12" t="n">
+        <v>3238</v>
+      </c>
+      <c r="W152" s="12" t="n">
+        <v>-322679</v>
+      </c>
+      <c r="X152" s="12" t="n">
+        <v>-96074</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 환산차이</t>
         </is>
       </c>
-      <c r="F111" s="22" t="n">
+      <c r="D153" s="22" t="n">
+        <v>874</v>
+      </c>
+      <c r="E153" s="22" t="n">
         <v>2746</v>
       </c>
-      <c r="J111" s="22" t="n">
+      <c r="F153" s="22" t="n">
+        <v>2533</v>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>-1204</v>
+      </c>
+      <c r="H153" s="22" t="n">
+        <v>2170</v>
+      </c>
+      <c r="I153" s="22" t="n">
         <v>-387</v>
       </c>
-      <c r="N111" s="22" t="n">
+      <c r="J153" s="22" t="n">
+        <v>782</v>
+      </c>
+      <c r="K153" s="22" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L153" s="22" t="n">
+        <v>3254</v>
+      </c>
+      <c r="M153" s="22" t="n">
         <v>3821</v>
       </c>
-      <c r="V111" s="22" t="n">
+      <c r="N153" s="22" t="n">
+        <v>1652</v>
+      </c>
+      <c r="V153" s="22" t="n">
         <v>2746</v>
       </c>
-      <c r="W111" s="22" t="n">
+      <c r="W153" s="22" t="n">
         <v>-387</v>
       </c>
-      <c r="X111" s="22" t="n">
+      <c r="X153" s="22" t="n">
         <v>3821</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="20" t="inlineStr">
         <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="F112" s="22" t="n">
+      <c r="D154" s="22" t="n">
+        <v>-51637</v>
+      </c>
+      <c r="E154" s="22" t="n">
         <v>-73758</v>
       </c>
-      <c r="J112" s="22" t="n">
+      <c r="F154" s="22" t="n">
+        <v>-17520</v>
+      </c>
+      <c r="G154" s="22" t="n">
+        <v>-43899</v>
+      </c>
+      <c r="H154" s="22" t="n">
+        <v>-13293</v>
+      </c>
+      <c r="I154" s="22" t="n">
         <v>-19661</v>
       </c>
-      <c r="N112" s="22" t="n">
+      <c r="J154" s="22" t="n">
+        <v>10489</v>
+      </c>
+      <c r="K154" s="22" t="n">
+        <v>67614</v>
+      </c>
+      <c r="L154" s="22" t="n">
+        <v>113595</v>
+      </c>
+      <c r="M154" s="22" t="n">
         <v>302775</v>
       </c>
-      <c r="V112" s="22" t="n">
+      <c r="N154" s="22" t="n">
+        <v>320307</v>
+      </c>
+      <c r="V154" s="22" t="n">
         <v>-73758</v>
       </c>
-      <c r="W112" s="22" t="n">
+      <c r="W154" s="22" t="n">
         <v>-19661</v>
       </c>
-      <c r="X112" s="22" t="n">
+      <c r="X154" s="22" t="n">
         <v>302775</v>
       </c>
     </row>
@@ -6197,7 +9244,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -6221,27 +9268,27 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -6284,13 +9331,17 @@
       </c>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="11" t="n">
-        <v>806709</v>
+        <v>890275</v>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
+      <c r="E5" s="12" t="n">
+        <v>1059602</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>1617829</v>
+      </c>
       <c r="G5" s="12" t="n">
-        <v>1617829</v>
+        <v>2471978</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>651375</v>
@@ -6310,13 +9361,17 @@
       </c>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="21" t="n">
-        <v>167932</v>
+        <v>235546</v>
       </c>
       <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
+      <c r="E6" s="22" t="n">
+        <v>281527</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>470707</v>
+      </c>
       <c r="G6" s="22" t="n">
-        <v>470707</v>
+        <v>791014</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>187593</v>
@@ -6336,13 +9391,17 @@
       </c>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="21" t="n">
-        <v>3971</v>
+        <v>3929</v>
       </c>
       <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
+      <c r="E7" s="22" t="n">
+        <v>7955</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>7191</v>
+      </c>
       <c r="G7" s="22" t="n">
-        <v>7191</v>
+        <v>4751</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>5353</v>
@@ -6362,13 +9421,17 @@
       </c>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="21" t="n">
-        <v>238594</v>
+        <v>236412</v>
       </c>
       <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
+      <c r="E8" s="22" t="n">
+        <v>347780</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>660559</v>
+      </c>
       <c r="G8" s="22" t="n">
-        <v>660559</v>
+        <v>1151562</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>149815</v>
@@ -6388,13 +9451,17 @@
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="21" t="n">
-        <v>352863</v>
+        <v>361634</v>
       </c>
       <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
+      <c r="E9" s="22" t="n">
+        <v>353486</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>412612</v>
+      </c>
       <c r="G9" s="22" t="n">
-        <v>412612</v>
+        <v>438111</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>271781</v>
@@ -6458,13 +9525,17 @@
       </c>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="11" t="n">
-        <v>2112970</v>
+        <v>2091944</v>
       </c>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
+      <c r="E11" s="12" t="n">
+        <v>2135240</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>2072242</v>
+      </c>
       <c r="G11" s="12" t="n">
-        <v>2072242</v>
+        <v>2258498</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>2213566</v>
@@ -6484,13 +9555,17 @@
       </c>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="21" t="n">
-        <v>1100181</v>
+        <v>1068664</v>
       </c>
       <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
+      <c r="E12" s="22" t="n">
+        <v>1056828</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>1055255</v>
+      </c>
       <c r="G12" s="22" t="n">
-        <v>1055255</v>
+        <v>1055840</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>1168765</v>
@@ -6510,13 +9585,17 @@
       </c>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="21" t="n">
-        <v>10658</v>
+        <v>11244</v>
       </c>
       <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
+      <c r="E13" s="22" t="n">
+        <v>11071</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>11192</v>
+      </c>
       <c r="G13" s="22" t="n">
-        <v>11192</v>
+        <v>11657</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>11259</v>
@@ -6596,13 +9675,17 @@
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="11" t="n">
-        <v>2919679</v>
+        <v>2982219</v>
       </c>
       <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
+      <c r="E16" s="12" t="n">
+        <v>3194842</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>3690071</v>
+      </c>
       <c r="G16" s="12" t="n">
-        <v>3690071</v>
+        <v>4730476</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>2864941</v>
@@ -6638,13 +9721,17 @@
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="11" t="n">
-        <v>985173</v>
+        <v>904439</v>
       </c>
       <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
+      <c r="E18" s="12" t="n">
+        <v>986360</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>1098008</v>
+      </c>
       <c r="G18" s="12" t="n">
-        <v>1098008</v>
+        <v>1395780</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>1866127</v>
@@ -6664,13 +9751,17 @@
       </c>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="21" t="n">
-        <v>504011</v>
+        <v>544641</v>
       </c>
       <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
+      <c r="E19" s="22" t="n">
+        <v>606755</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>594917</v>
+      </c>
       <c r="G19" s="22" t="n">
-        <v>594917</v>
+        <v>706802</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>512502</v>
@@ -6690,7 +9781,7 @@
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="21" t="n">
-        <v>246508</v>
+        <v>261820</v>
       </c>
       <c r="D20" s="22" t="n"/>
       <c r="E20" s="22" t="n"/>
@@ -6772,13 +9863,17 @@
       </c>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="n">
-        <v>1196810</v>
+        <v>1258438</v>
       </c>
       <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
+      <c r="E23" s="12" t="n">
+        <v>1229835</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>1192984</v>
+      </c>
       <c r="G23" s="12" t="n">
-        <v>1192984</v>
+        <v>930218</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>549048</v>
@@ -6798,7 +9893,7 @@
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="21" t="n">
-        <v>531198</v>
+        <v>507057</v>
       </c>
       <c r="D24" s="22" t="n"/>
       <c r="E24" s="22" t="n"/>
@@ -6820,13 +9915,17 @@
       </c>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="21" t="n">
-        <v>531198</v>
+        <v>920910</v>
       </c>
       <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
+      <c r="E25" s="22" t="n">
+        <v>900872</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>872116</v>
+      </c>
       <c r="G25" s="22" t="n">
-        <v>872116</v>
+        <v>543009</v>
       </c>
       <c r="H25" s="21" t="n"/>
       <c r="I25" s="22" t="n">
@@ -6888,13 +9987,17 @@
       </c>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="n">
-        <v>2181983</v>
+        <v>2162877</v>
       </c>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
+      <c r="E27" s="12" t="n">
+        <v>2216195</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>2290992</v>
+      </c>
       <c r="G27" s="12" t="n">
-        <v>2290992</v>
+        <v>2325998</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>2415175</v>
@@ -7018,13 +10121,17 @@
       </c>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="n">
-        <v>737565</v>
+        <v>819203</v>
       </c>
       <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
+      <c r="E31" s="12" t="n">
+        <v>978502</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>1398929</v>
+      </c>
       <c r="G31" s="12" t="n">
-        <v>1398929</v>
+        <v>2404320</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>449635</v>
@@ -7044,13 +10151,17 @@
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="21" t="n">
-        <v>25239</v>
+        <v>25578</v>
       </c>
       <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
+      <c r="E32" s="22" t="n">
+        <v>29880</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>31284</v>
+      </c>
       <c r="G32" s="22" t="n">
-        <v>31284</v>
+        <v>33133</v>
       </c>
       <c r="H32" s="21" t="n">
         <v>10000</v>
@@ -7070,13 +10181,17 @@
       </c>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="21" t="n">
-        <v>-189547</v>
+        <v>-130594</v>
       </c>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
+      <c r="E33" s="22" t="n">
+        <v>-42784</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>366955</v>
+      </c>
       <c r="G33" s="22" t="n">
-        <v>366955</v>
+        <v>1209116</v>
       </c>
       <c r="H33" s="21" t="n">
         <v>-463054</v>
@@ -7096,13 +10211,17 @@
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="21" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
+      <c r="E34" s="22" t="n">
+        <v>145</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>150</v>
+      </c>
       <c r="G34" s="22" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H34" s="21" t="n">
         <v>131</v>
@@ -7122,13 +10241,17 @@
       </c>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="n">
-        <v>737696</v>
+        <v>819342</v>
       </c>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
+      <c r="E35" s="12" t="n">
+        <v>978647</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>1399079</v>
+      </c>
       <c r="G35" s="12" t="n">
-        <v>1399079</v>
+        <v>2404478</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>449766</v>
@@ -7168,13 +10291,19 @@
       </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="n">
-        <v>476416</v>
-      </c>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
+        <v>442380</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>409703</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>426023</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>616540</v>
+      </c>
       <c r="G37" s="12" t="n">
-        <v>616540</v>
+        <v>1421771</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>195111</v>
@@ -7198,13 +10327,19 @@
         </is>
       </c>
       <c r="C38" s="21" t="n">
-        <v>225603</v>
-      </c>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
+        <v>233014</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>283197</v>
+      </c>
+      <c r="E38" s="22" t="n">
+        <v>296284</v>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>283674</v>
+      </c>
       <c r="G38" s="22" t="n">
-        <v>283674</v>
+        <v>282499</v>
       </c>
       <c r="H38" s="21" t="n">
         <v>305097</v>
@@ -7313,7 +10448,7 @@
       <c r="J42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -7357,7 +10492,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -7401,7 +10536,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -7445,7 +10580,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -7489,7 +10624,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -7533,7 +10668,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -7577,7 +10712,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -7587,35 +10722,35 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",H28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",I28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",J28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -7637,7 +10772,7 @@
       <c r="J50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -7681,7 +10816,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -7725,7 +10860,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -7769,7 +10904,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -7813,7 +10948,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -7857,7 +10992,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -7917,7 +11052,7 @@
       <c r="J57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -7961,7 +11096,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -7971,41 +11106,41 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -8015,41 +11150,41 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -8059,41 +11194,41 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -8103,35 +11238,35 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
@@ -8153,7 +11288,7 @@
       <c r="J63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -8197,7 +11332,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -8241,7 +11376,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -8285,7 +11420,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -8361,27 +11496,27 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -8407,10 +11542,16 @@
         </is>
       </c>
       <c r="C71" s="22" t="n">
-        <v>167932</v>
+        <v>235546</v>
+      </c>
+      <c r="E71" s="22" t="n">
+        <v>281527</v>
+      </c>
+      <c r="F71" s="22" t="n">
+        <v>470707</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>470707</v>
+        <v>791014</v>
       </c>
       <c r="H71" s="22" t="n">
         <v>187593</v>
@@ -8429,10 +11570,16 @@
         </is>
       </c>
       <c r="C72" s="22" t="n">
-        <v>238594</v>
+        <v>236412</v>
+      </c>
+      <c r="E72" s="22" t="n">
+        <v>347780</v>
+      </c>
+      <c r="F72" s="22" t="n">
+        <v>660559</v>
       </c>
       <c r="G72" s="22" t="n">
-        <v>660559</v>
+        <v>1151562</v>
       </c>
       <c r="H72" s="22" t="n">
         <v>149815</v>
@@ -8451,10 +11598,16 @@
         </is>
       </c>
       <c r="C73" s="22" t="n">
-        <v>3971</v>
+        <v>3929</v>
+      </c>
+      <c r="E73" s="22" t="n">
+        <v>7955</v>
+      </c>
+      <c r="F73" s="22" t="n">
+        <v>7191</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>7191</v>
+        <v>4751</v>
       </c>
       <c r="H73" s="22" t="n">
         <v>5353</v>
@@ -8473,10 +11626,16 @@
         </is>
       </c>
       <c r="C74" s="22" t="n">
-        <v>352863</v>
+        <v>361634</v>
+      </c>
+      <c r="E74" s="22" t="n">
+        <v>353486</v>
+      </c>
+      <c r="F74" s="22" t="n">
+        <v>412612</v>
       </c>
       <c r="G74" s="22" t="n">
-        <v>412612</v>
+        <v>438111</v>
       </c>
       <c r="H74" s="22" t="n">
         <v>271781</v>
@@ -8495,10 +11654,16 @@
         </is>
       </c>
       <c r="C75" s="22" t="n">
-        <v>43349</v>
+        <v>52754</v>
+      </c>
+      <c r="E75" s="22" t="n">
+        <v>68854</v>
+      </c>
+      <c r="F75" s="22" t="n">
+        <v>66760</v>
       </c>
       <c r="G75" s="22" t="n">
-        <v>66760</v>
+        <v>86540</v>
       </c>
       <c r="H75" s="22" t="n">
         <v>36833</v>
@@ -8517,10 +11682,16 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>806709</v>
+        <v>890275</v>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>1059602</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>1617829</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1617829</v>
+        <v>2471978</v>
       </c>
       <c r="H76" s="12" t="n">
         <v>651375</v>
@@ -8539,10 +11710,16 @@
         </is>
       </c>
       <c r="C77" s="22" t="n">
-        <v>1100181</v>
+        <v>1068664</v>
+      </c>
+      <c r="E77" s="22" t="n">
+        <v>1056828</v>
+      </c>
+      <c r="F77" s="22" t="n">
+        <v>1055255</v>
       </c>
       <c r="G77" s="22" t="n">
-        <v>1055255</v>
+        <v>1055840</v>
       </c>
       <c r="H77" s="22" t="n">
         <v>1168765</v>
@@ -8561,10 +11738,16 @@
         </is>
       </c>
       <c r="C78" s="22" t="n">
-        <v>197063</v>
+        <v>192407</v>
+      </c>
+      <c r="E78" s="22" t="n">
+        <v>186408</v>
+      </c>
+      <c r="F78" s="22" t="n">
+        <v>178092</v>
       </c>
       <c r="G78" s="22" t="n">
-        <v>178092</v>
+        <v>175510</v>
       </c>
       <c r="H78" s="22" t="n">
         <v>159719</v>
@@ -8583,10 +11766,16 @@
         </is>
       </c>
       <c r="C79" s="22" t="n">
-        <v>395256</v>
+        <v>395511</v>
+      </c>
+      <c r="E79" s="22" t="n">
+        <v>395577</v>
+      </c>
+      <c r="F79" s="22" t="n">
+        <v>395585</v>
       </c>
       <c r="G79" s="22" t="n">
-        <v>395585</v>
+        <v>395660</v>
       </c>
       <c r="H79" s="22" t="n">
         <v>395405</v>
@@ -8605,10 +11794,16 @@
         </is>
       </c>
       <c r="C80" s="22" t="n">
-        <v>10658</v>
+        <v>11244</v>
+      </c>
+      <c r="E80" s="22" t="n">
+        <v>11071</v>
+      </c>
+      <c r="F80" s="22" t="n">
+        <v>11192</v>
       </c>
       <c r="G80" s="22" t="n">
-        <v>11192</v>
+        <v>11657</v>
       </c>
       <c r="H80" s="22" t="n">
         <v>11259</v>
@@ -8627,10 +11822,16 @@
         </is>
       </c>
       <c r="C81" s="22" t="n">
-        <v>7401</v>
+        <v>7285</v>
+      </c>
+      <c r="E81" s="22" t="n">
+        <v>7441</v>
+      </c>
+      <c r="F81" s="22" t="n">
+        <v>8097</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>8097</v>
+        <v>8434</v>
       </c>
       <c r="H81" s="22" t="n">
         <v>6869</v>
@@ -8649,10 +11850,16 @@
         </is>
       </c>
       <c r="C82" s="22" t="n">
-        <v>63179</v>
+        <v>93200</v>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>198068</v>
+      </c>
+      <c r="F82" s="22" t="n">
+        <v>219230</v>
       </c>
       <c r="G82" s="22" t="n">
-        <v>219230</v>
+        <v>522327</v>
       </c>
       <c r="H82" s="22" t="n">
         <v>87139</v>
@@ -8671,10 +11878,16 @@
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>20069</v>
+        <v>27030</v>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>29330</v>
+      </c>
+      <c r="F83" s="22" t="n">
+        <v>27285</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>27285</v>
+        <v>26019</v>
       </c>
       <c r="H83" s="22" t="n">
         <v>13688</v>
@@ -8693,10 +11906,16 @@
         </is>
       </c>
       <c r="C84" s="22" t="n">
-        <v>319163</v>
+        <v>296603</v>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>250517</v>
+      </c>
+      <c r="F84" s="22" t="n">
+        <v>177506</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>177506</v>
+        <v>63051</v>
       </c>
       <c r="H84" s="22" t="n">
         <v>370722</v>
@@ -8715,10 +11934,16 @@
         </is>
       </c>
       <c r="C85" s="22" t="n">
-        <v>2112970</v>
+        <v>2091944</v>
+      </c>
+      <c r="E85" s="22" t="n">
+        <v>2135240</v>
+      </c>
+      <c r="F85" s="22" t="n">
+        <v>2072242</v>
       </c>
       <c r="G85" s="22" t="n">
-        <v>2072242</v>
+        <v>2258498</v>
       </c>
       <c r="H85" s="22" t="n">
         <v>2213566</v>
@@ -8737,10 +11962,16 @@
         </is>
       </c>
       <c r="C86" s="22" t="n">
-        <v>2919679</v>
+        <v>2982219</v>
+      </c>
+      <c r="E86" s="22" t="n">
+        <v>3194842</v>
+      </c>
+      <c r="F86" s="22" t="n">
+        <v>3690071</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>3690071</v>
+        <v>4730476</v>
       </c>
       <c r="H86" s="22" t="n">
         <v>2864941</v>
@@ -8759,7 +11990,7 @@
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>246508</v>
+        <v>261820</v>
       </c>
       <c r="H87" s="22" t="n">
         <v>826413</v>
@@ -8775,10 +12006,16 @@
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>246508</v>
+        <v>189224</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>185170</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>175452</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>175452</v>
+        <v>91545</v>
       </c>
       <c r="I88" s="22" t="n">
         <v>246508</v>
@@ -8794,10 +12031,16 @@
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>504011</v>
+        <v>544641</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>606755</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>594917</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>594917</v>
+        <v>706802</v>
       </c>
       <c r="H89" s="22" t="n">
         <v>512502</v>
@@ -8816,10 +12059,16 @@
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>42521</v>
+        <v>44244</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>44621</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>43911</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>43911</v>
+        <v>43544</v>
       </c>
       <c r="H90" s="22" t="n">
         <v>40025</v>
@@ -8838,10 +12087,16 @@
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>28058</v>
+        <v>7422</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>18329</v>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>28338</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>28338</v>
+        <v>36743</v>
       </c>
       <c r="H91" s="22" t="n">
         <v>344341</v>
@@ -8860,10 +12115,16 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>38183</v>
+        <v>10886</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>8706</v>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>104516</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>104516</v>
+        <v>340035</v>
       </c>
       <c r="H92" s="22" t="n">
         <v>6182</v>
@@ -8882,10 +12143,16 @@
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>3328</v>
+        <v>2179</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>3876</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>3876</v>
+        <v>7650</v>
       </c>
       <c r="H93" s="22" t="n">
         <v>4694</v>
@@ -8904,10 +12171,16 @@
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>122564</v>
+        <v>105843</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>120700</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>146998</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>146998</v>
+        <v>169461</v>
       </c>
       <c r="H94" s="22" t="n">
         <v>131970</v>
@@ -8926,10 +12199,16 @@
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>985173</v>
+        <v>904439</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>986360</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>1098008</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>1098008</v>
+        <v>1395780</v>
       </c>
       <c r="H95" s="22" t="n">
         <v>1866127</v>
@@ -8948,7 +12227,7 @@
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>531198</v>
+        <v>507057</v>
       </c>
       <c r="H96" s="22" t="n">
         <v>284899</v>
@@ -8964,10 +12243,16 @@
         </is>
       </c>
       <c r="C97" s="22" t="n">
-        <v>531198</v>
+        <v>920910</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>900872</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>872116</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>872116</v>
+        <v>543009</v>
       </c>
       <c r="I97" s="22" t="n">
         <v>531198</v>
@@ -8983,10 +12268,16 @@
         </is>
       </c>
       <c r="C98" s="22" t="n">
-        <v>179294</v>
+        <v>175172</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>169177</v>
+      </c>
+      <c r="F98" s="22" t="n">
+        <v>161710</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>161710</v>
+        <v>159733</v>
       </c>
       <c r="H98" s="22" t="n">
         <v>142871</v>
@@ -9005,9 +12296,12 @@
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>321261</v>
-      </c>
-      <c r="G99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="22" t="n">
@@ -9027,10 +12321,16 @@
         </is>
       </c>
       <c r="C100" s="22" t="n">
-        <v>46477</v>
+        <v>46138</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>46067</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>42871</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>42871</v>
+        <v>42842</v>
       </c>
       <c r="H100" s="22" t="n">
         <v>48492</v>
@@ -9049,10 +12349,16 @@
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>7560</v>
+        <v>8379</v>
+      </c>
+      <c r="E101" s="22" t="n">
+        <v>9727</v>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>12840</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>12840</v>
+        <v>58335</v>
       </c>
       <c r="H101" s="22" t="n">
         <v>7331</v>
@@ -9071,10 +12377,16 @@
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>111017</v>
+        <v>107836</v>
+      </c>
+      <c r="E102" s="22" t="n">
+        <v>103425</v>
+      </c>
+      <c r="F102" s="22" t="n">
+        <v>102725</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>102725</v>
+        <v>119630</v>
       </c>
       <c r="H102" s="22" t="n">
         <v>65419</v>
@@ -9095,8 +12407,14 @@
       <c r="C103" s="22" t="n">
         <v>3</v>
       </c>
+      <c r="E103" s="22" t="n">
+        <v>567</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>722</v>
+      </c>
       <c r="G103" s="22" t="n">
-        <v>722</v>
+        <v>6669</v>
       </c>
       <c r="H103" s="22" t="n">
         <v>36</v>
@@ -9115,10 +12433,16 @@
         </is>
       </c>
       <c r="C104" s="22" t="n">
-        <v>1196810</v>
+        <v>1258438</v>
+      </c>
+      <c r="E104" s="22" t="n">
+        <v>1229835</v>
+      </c>
+      <c r="F104" s="22" t="n">
+        <v>1192984</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>1192984</v>
+        <v>930218</v>
       </c>
       <c r="H104" s="22" t="n">
         <v>549048</v>
@@ -9137,10 +12461,16 @@
         </is>
       </c>
       <c r="C105" s="22" t="n">
-        <v>2181983</v>
+        <v>2162877</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>2216195</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>2290992</v>
       </c>
       <c r="G105" s="22" t="n">
-        <v>2290992</v>
+        <v>2325998</v>
       </c>
       <c r="H105" s="22" t="n">
         <v>2415175</v>
@@ -9159,10 +12489,16 @@
         </is>
       </c>
       <c r="C106" s="22" t="n">
-        <v>25239</v>
+        <v>25578</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>29880</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>31284</v>
       </c>
       <c r="G106" s="22" t="n">
-        <v>31284</v>
+        <v>33133</v>
       </c>
       <c r="H106" s="22" t="n">
         <v>10000</v>
@@ -9181,10 +12517,16 @@
         </is>
       </c>
       <c r="C107" s="22" t="n">
-        <v>866665</v>
+        <v>867701</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>872637</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>875804</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>875804</v>
+        <v>883711</v>
       </c>
       <c r="H107" s="22" t="n">
         <v>851517</v>
@@ -9203,10 +12545,16 @@
         </is>
       </c>
       <c r="C108" s="22" t="n">
-        <v>35208</v>
+        <v>56518</v>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>118769</v>
+      </c>
+      <c r="F108" s="22" t="n">
+        <v>124888</v>
       </c>
       <c r="G108" s="22" t="n">
-        <v>124888</v>
+        <v>278380</v>
       </c>
       <c r="H108" s="22" t="n">
         <v>51172</v>
@@ -9225,10 +12573,16 @@
         </is>
       </c>
       <c r="C109" s="22" t="n">
-        <v>-189547</v>
+        <v>-130594</v>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>-42784</v>
+      </c>
+      <c r="F109" s="22" t="n">
+        <v>366955</v>
       </c>
       <c r="G109" s="22" t="n">
-        <v>366955</v>
+        <v>1209116</v>
       </c>
       <c r="H109" s="22" t="n">
         <v>-463054</v>
@@ -9246,11 +12600,14 @@
           <t>자기주식</t>
         </is>
       </c>
-      <c r="C110" s="22" t="n">
-        <v>0</v>
+      <c r="E110" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>-2</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>-2</v>
+        <v>-20</v>
       </c>
       <c r="I110" s="22" t="n">
         <v>0</v>
@@ -9266,10 +12623,16 @@
         </is>
       </c>
       <c r="C111" s="22" t="n">
-        <v>737565</v>
+        <v>819203</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>978502</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>1398929</v>
       </c>
       <c r="G111" s="22" t="n">
-        <v>1398929</v>
+        <v>2404320</v>
       </c>
       <c r="H111" s="22" t="n">
         <v>449635</v>
@@ -9288,10 +12651,16 @@
         </is>
       </c>
       <c r="C112" s="22" t="n">
-        <v>131</v>
+        <v>139</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>145</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>150</v>
       </c>
       <c r="G112" s="22" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H112" s="22" t="n">
         <v>131</v>
@@ -9310,10 +12679,16 @@
         </is>
       </c>
       <c r="C113" s="22" t="n">
-        <v>737696</v>
+        <v>819342</v>
+      </c>
+      <c r="E113" s="22" t="n">
+        <v>978647</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>1399079</v>
       </c>
       <c r="G113" s="22" t="n">
-        <v>1399079</v>
+        <v>2404478</v>
       </c>
       <c r="H113" s="22" t="n">
         <v>449766</v>
@@ -9332,10 +12707,16 @@
         </is>
       </c>
       <c r="C114" s="22" t="n">
-        <v>2919679</v>
+        <v>2982219</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>3194842</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>3690071</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>3690071</v>
+        <v>4730476</v>
       </c>
       <c r="H114" s="22" t="n">
         <v>2864941</v>
@@ -9434,7 +12815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9443,24 +12824,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -9469,34 +12850,119 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 연간 결산단신</t>
+          <t>2027년 3월 결산기 １분기 결산단신</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/285A0/140120260515537803.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/285A0/140120260731505265.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026년 3월 결산기 연간 결산단신</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/285A0/140120260515537803.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026년 3월 결산기 ３분기 결산단신</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/285A0/140120260212556330.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026년 3월 결산기 ２분기 결산단신</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/285A0/140120251113599856.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026년 3월 결산기 １분기 결산단신</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/285A0/140120250808536248.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2025년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://www2.jpx.co.jp/disc/285A0/140120250515552869.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025년 3월 결산기 ３분기 결산단신</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/285A0/140120250207566970.pdf</t>
         </is>
       </c>
     </row>

--- a/docs/data/jp/xlsx/285A.xlsx
+++ b/docs/data/jp/xlsx/285A.xlsx
@@ -8640,7 +8640,7 @@
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>Net Change In Fair Value Of Equity Instruments Designated As Measured At Fair Value Through Other Comprehensive Income Net Of Tax Items That Will Not Be Reclassified To Profit Or Loss OCI</t>
+          <t>기타포괄손익-공정가치 측정 금융자산 순변동</t>
         </is>
       </c>
       <c r="D116" s="22" t="n">
@@ -8836,7 +8836,7 @@
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>Effective Portion Of Cash Flow Hedges Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+          <t>현금흐름 위험회피 유효 부분</t>
         </is>
       </c>
       <c r="D120" s="22" t="n">
@@ -8885,7 +8885,7 @@
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>Share Of Other Comprehensive Income Of Investments Accounted For Using Equity Method Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+          <t>지분법 적용회사 기타포괄이익 지분</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
@@ -10145,7 +10145,7 @@
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>Income Taxes Refund Paid Ope CF</t>
+          <t>법인소득세 지급액 또는 환급액(△는 지급)</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
@@ -10590,7 +10590,7 @@
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Short Term Borrowings And Revolving Credit Facility Balances Executed Fin CF</t>
+          <t>단기차입금 및 리볼빙 신용한도 실행 잔액 순증감액(△는 감소)</t>
         </is>
       </c>
       <c r="F155" s="22" t="n">
@@ -10655,7 +10655,7 @@
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Long Term Borrowings Fin CF</t>
+          <t>장기차입 수입</t>
         </is>
       </c>
       <c r="C157" s="22" t="n">
@@ -10845,7 +10845,7 @@
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>Redemption Of Preferred Shares Fin CF</t>
+          <t>우선주 상환 지출</t>
         </is>
       </c>
       <c r="F161" s="22" t="n">
